--- a/artfynd/A 5611-2026 artfynd.xlsx
+++ b/artfynd/A 5611-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340282</v>
       </c>
       <c r="B2" t="n">
-        <v>80229</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
